--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487946_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487946_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.973</v>
+        <v>5.0924</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7874</v>
+        <v>2.3842</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1856</v>
+        <v>2.7083</v>
       </c>
       <c r="G2" t="n">
         <v>3.1285</v>
@@ -610,13 +610,13 @@
         <v>2.3787</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8555</v>
+        <v>1.9749</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3459</v>
+        <v>0.9427</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5096</v>
+        <v>1.0322</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4074</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.914</v>
+        <v>4.1115</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1702</v>
+        <v>3.48</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7438</v>
+        <v>0.6315</v>
       </c>
       <c r="G3" t="n">
         <v>0.9370000000000001</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4507</v>
+        <v>1.6482</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7916</v>
+        <v>1.1014</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6591</v>
+        <v>0.5468</v>
       </c>
       <c r="V3" t="n">
         <v>0.337</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1775</v>
+        <v>2.0995</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4347</v>
+        <v>0.4971</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7428</v>
+        <v>1.6024</v>
       </c>
       <c r="G4" t="n">
         <v>0.656</v>
@@ -766,13 +766,13 @@
         <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9268</v>
+        <v>0.8488</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0552</v>
+        <v>0.1176</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8717</v>
+        <v>0.7313</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2078</v>
+        <v>1.7172</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0951</v>
+        <v>0.6045</v>
       </c>
       <c r="F5" t="n">
         <v>1.1127</v>
@@ -844,10 +844,10 @@
         <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.011</v>
+        <v>0.4983</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2496</v>
+        <v>0.2598</v>
       </c>
       <c r="U5" t="n">
         <v>0.2386</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7156</v>
+        <v>0.9537</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1891</v>
+        <v>0.0771</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.8766</v>
       </c>
       <c r="G6" t="n">
         <v>0.7454</v>
@@ -922,13 +922,13 @@
         <v>0.1982</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.228</v>
+        <v>0.0101</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2496</v>
+        <v>0.0165</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0216</v>
+        <v>-0.0065</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7846</v>
+        <v>-0.7897</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2206</v>
+        <v>0.2435</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0052</v>
+        <v>-1.0332</v>
       </c>
       <c r="G7" t="n">
         <v>0.0279</v>
@@ -1000,13 +1000,13 @@
         <v>1.1893</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4776</v>
+        <v>-0.4827</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.132</v>
+        <v>-0.1091</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3455</v>
+        <v>-0.3736</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5331</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5814</v>
+        <v>-1.5671</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3112</v>
+        <v>-1.2574</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7298</v>
+        <v>-0.3096</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1684</v>
+        <v>0.7359</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.0857</v>
+        <v>0.2918</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0827</v>
+        <v>0.444</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3862</v>
+        <v>1.7062</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5581</v>
+        <v>1.285</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.8282</v>
+        <v>0.4212</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7822</v>
+        <v>-0.9704</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5276</v>
+        <v>-0.9932</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2545</v>
+        <v>0.0228</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>-1.784</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3876</v>
+        <v>2.1805</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1905</v>
+        <v>-0.2523</v>
       </c>
       <c r="T8" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2063</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1243</v>
+        <v>-0.046</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0745</v>
+        <v>-1.7508</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4841</v>
+        <v>-2.4525</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5904</v>
+        <v>0.7017</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7359</v>
+        <v>-2.1684</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2918</v>
+        <v>-1.0857</v>
       </c>
       <c r="I9" t="n">
-        <v>0.444</v>
+        <v>-1.0827</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7062</v>
+        <v>-1.3862</v>
       </c>
       <c r="K9" t="n">
-        <v>1.285</v>
+        <v>-0.5581</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4212</v>
+        <v>-0.8282</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9704</v>
+        <v>-0.7822</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9932</v>
+        <v>-0.5276</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0228</v>
+        <v>-0.2545</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R9" t="n">
-        <v>2.1805</v>
+        <v>1.3876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7598</v>
+        <v>0.0211</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.433</v>
+        <v>-0.0752</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3268</v>
+        <v>0.0963</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3959</v>
+        <v>-2.1087</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7628</v>
+        <v>-2.9249</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3669</v>
+        <v>0.8162</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5176</v>
@@ -1234,13 +1234,13 @@
         <v>3.1716</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5851</v>
+        <v>0.7020999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6826</v>
+        <v>0.1553</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0975</v>
+        <v>0.5468</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4737</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6324</v>
+        <v>-2.8393</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8432</v>
+        <v>-2.9659</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2108</v>
+        <v>0.1266</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1092</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2764</v>
+        <v>0.5167</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8112</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5347</v>
+        <v>0.4505</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4627</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.519100000000002</v>
+        <v>4.918700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.882399999999999</v>
+        <v>-2.314300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>7.4015</v>
+        <v>7.2332</v>
       </c>
       <c r="G12" t="n">
         <v>0.5859999999999999</v>
@@ -1390,13 +1390,13 @@
         <v>16.2544</v>
       </c>
       <c r="S12" t="n">
-        <v>5.085600000000001</v>
+        <v>5.4852</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7009</v>
+        <v>2.2689</v>
       </c>
       <c r="U12" t="n">
-        <v>3.3848</v>
+        <v>3.216399999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5399</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>C. VARGAS VIVANCO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5014</v>
+        <v>0.7955</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6325</v>
+        <v>-1.2194</v>
       </c>
       <c r="F13" t="n">
-        <v>0.869</v>
+        <v>2.0149</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2957</v>
+        <v>0.0368</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9246</v>
+        <v>0.0521</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2204</v>
+        <v>-0.0153</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5238</v>
+        <v>0.7413</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0774</v>
+        <v>1.4528</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4464</v>
+        <v>-0.7115</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2281</v>
+        <v>-0.7044</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.0021</v>
+        <v>-1.4007</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.226</v>
+        <v>0.6962</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3964</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q13" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5769</v>
+        <v>2.1805</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1394</v>
+        <v>-0.3295</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3527</v>
+        <v>-0.1944</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7868000000000001</v>
+        <v>-0.135</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4627</v>
+        <v>1.8811</v>
       </c>
       <c r="W13" t="n">
-        <v>0.7292999999999999</v>
+        <v>1.2071</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. VARGAS VIVANCO</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8236</v>
+        <v>0.373</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.2194</v>
+        <v>-0.1825</v>
       </c>
       <c r="F14" t="n">
-        <v>2.043</v>
+        <v>0.5555</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0368</v>
+        <v>0.2957</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0521</v>
+        <v>-0.9246</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0153</v>
+        <v>1.2204</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7413</v>
+        <v>2.5238</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4528</v>
+        <v>1.0774</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7115</v>
+        <v>1.4464</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7044</v>
+        <v>-2.2281</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4007</v>
+        <v>-2.0021</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6962</v>
+        <v>-0.226</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7929</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q14" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1805</v>
+        <v>2.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3014</v>
+        <v>0.011</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1944</v>
+        <v>-0.4623</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.107</v>
+        <v>0.4733</v>
       </c>
       <c r="V14" t="n">
-        <v>1.8811</v>
+        <v>0.4627</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2071</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. YELAMOS MANAS</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5919</v>
+        <v>0.3184</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.5485</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1405</v>
+        <v>0.3184</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5395</v>
+        <v>0.2717</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5734</v>
+        <v>0.1358</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9661</v>
+        <v>0.1358</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.374</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.222</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.596</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8346</v>
+        <v>0.2717</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7953</v>
+        <v>0.1358</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6299</v>
+        <v>0.1358</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4574</v>
+        <v>0.0468</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6095</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1521</v>
+        <v>0.0468</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2775</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2904</v>
+        <v>0.287</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-1.0752</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2904</v>
+        <v>1.3623</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2717</v>
+        <v>1.6437</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1358</v>
+        <v>1.1787</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1358</v>
+        <v>0.465</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.787</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>3.041</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.254</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2717</v>
+        <v>-1.1433</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1358</v>
+        <v>-1.8623</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1358</v>
+        <v>0.719</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0187</v>
+        <v>-0.9691</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.7679</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0187</v>
+        <v>-0.2012</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.8701</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>J. YELAMOS MANAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.1492</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2369</v>
+        <v>-2.1598</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1374</v>
+        <v>2.3089</v>
       </c>
       <c r="G17" t="n">
-        <v>1.568</v>
+        <v>-1.5395</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4031</v>
+        <v>-0.5734</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9711</v>
+        <v>-0.9661</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4585</v>
+        <v>-2.374</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3972</v>
+        <v>0.222</v>
       </c>
       <c r="L17" t="n">
-        <v>3.0613</v>
+        <v>-2.596</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8905</v>
+        <v>0.8346</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8003</v>
+        <v>-0.7953</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0902</v>
+        <v>1.6299</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9645</v>
+        <v>-0.9911</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1805</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4166</v>
+        <v>0.0147</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2641</v>
+        <v>-0.0017</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1525</v>
+        <v>0.0164</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5331</v>
+        <v>1.2775</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5331</v>
+        <v>1.2071</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DIARRA</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3103</v>
+        <v>-0.4097</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0165</v>
+        <v>-0.5425</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3268</v>
+        <v>0.1328</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7887999999999999</v>
+        <v>1.568</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6014</v>
+        <v>-1.4031</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1874</v>
+        <v>2.9711</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5068</v>
+        <v>3.4585</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4666</v>
+        <v>0.3972</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>3.0613</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.718</v>
+        <v>-1.8905</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8652</v>
+        <v>-1.8003</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1472</v>
+        <v>-0.0902</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3964</v>
+        <v>-1.784</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-3.9645</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5947</v>
+        <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7026</v>
+        <v>-0.7268</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4992</v>
+        <v>-0.5697</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2035</v>
+        <v>-0.1571</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>M. DIARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7375</v>
+        <v>-0.4226</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.992</v>
+        <v>0.0165</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2545</v>
+        <v>-0.4391</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6437</v>
+        <v>0.7887999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1787</v>
+        <v>0.6014</v>
       </c>
       <c r="I19" t="n">
-        <v>0.465</v>
+        <v>0.1874</v>
       </c>
       <c r="J19" t="n">
-        <v>2.787</v>
+        <v>1.5068</v>
       </c>
       <c r="K19" t="n">
-        <v>3.041</v>
+        <v>1.4666</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.254</v>
+        <v>0.0402</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1433</v>
+        <v>-0.718</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8623</v>
+        <v>-0.8652</v>
       </c>
       <c r="O19" t="n">
-        <v>0.719</v>
+        <v>0.1472</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.3964</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9911</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.9645</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.9733</v>
+        <v>0.5947</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9937</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.6847</v>
+        <v>-0.4992</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.309</v>
+        <v>-0.3158</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8701</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0015</v>
+        <v>-2.2617</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0302</v>
+        <v>-0.6227</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9714</v>
+        <v>-1.639</v>
       </c>
       <c r="G20" t="n">
         <v>-1.6114</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7667</v>
+        <v>-1.0269</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2479</v>
+        <v>-0.8405</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5188</v>
+        <v>-0.1864</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0109</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7931</v>
+        <v>-2.8848</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2669</v>
+        <v>-1.8595</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5262</v>
+        <v>-1.0253</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7355</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4452</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6312</v>
+        <v>-0.2237</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8139999999999999</v>
+        <v>-0.3131</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.734599999999999</v>
+        <v>-4.0557</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.6449</v>
+        <v>-7.6451</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9104</v>
+        <v>3.5894</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2817000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>14.8669</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.0107</v>
+        <v>-4.3316</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.559299999999999</v>
+        <v>-3.5594</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.4514</v>
+        <v>-0.7721</v>
       </c>
       <c r="V22" t="n">
         <v>2.54</v>
